--- a/files/R01-R69全节点业务验收测试包/S03_焊缝返修与热处理/S03_S03-WELDLOG-001_TEST-S03-004_焊口施焊台账.xlsx
+++ b/files/R01-R69全节点业务验收测试包/S03_焊缝返修与热处理/S03_S03-WELDLOG-001_TEST-S03-004_焊口施焊台账.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="施焊台账" sheetId="1" r:id="R423e8b4953b1414a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="异常时间线" sheetId="2" r:id="R64118a9728114388"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="施焊台账" sheetId="1" r:id="R640e4ba6fc13473b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="异常时间线" sheetId="2" r:id="R51aafb9a9f6f40b3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43,7 +43,7 @@
       <x:name val="Arial Unicode MS"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -60,8 +60,13 @@
         <x:fgColor rgb="FFFCE8E6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3F1"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="17">
     <x:border/>
     <x:border>
       <x:left/>
@@ -90,12 +95,64 @@
     <x:border>
       <x:right/>
       <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="69">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -187,6 +244,70 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -238,6 +359,70 @@
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="876300"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="f3f3bfeb-2bf6-47e2-805a-fd931bfceb98"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R2ab283b64fc0483f"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="876300"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="c8b1b004-50fb-44b5-9ca6-225845a17bad"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra3f44b4f7a2b48fc"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -583,11 +768,51 @@
       </x:c>
     </x:row>
     <x:row r="9"/>
-    <x:row r="10"/>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="60" t="str">
+        <x:v>电子签署（测试）｜工程质量测试专用章</x:v>
+      </x:c>
+      <x:c r="B10" s="61"/>
+      <x:c r="C10" s="61"/>
+      <x:c r="D10" s="61"/>
+      <x:c r="E10" s="61"/>
+      <x:c r="F10" s="61"/>
+      <x:c r="G10" s="62"/>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="63"/>
+      <x:c r="B11" s="64"/>
+      <x:c r="C11" s="64"/>
+      <x:c r="D11" s="64"/>
+      <x:c r="E11" s="64"/>
+      <x:c r="F11" s="64"/>
+      <x:c r="G11" s="65"/>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="63"/>
+      <x:c r="B12" s="64"/>
+      <x:c r="C12" s="64"/>
+      <x:c r="D12" s="64"/>
+      <x:c r="E12" s="64"/>
+      <x:c r="F12" s="64"/>
+      <x:c r="G12" s="65"/>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="66"/>
+      <x:c r="B13" s="67"/>
+      <x:c r="C13" s="67"/>
+      <x:c r="D13" s="67"/>
+      <x:c r="E13" s="67"/>
+      <x:c r="F13" s="67"/>
+      <x:c r="G13" s="68"/>
+    </x:row>
+    <x:row r="14"/>
+    <x:row r="15"/>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
     <x:mergeCell ref="A2:G2"/>
+    <x:mergeCell ref="A10:C10"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A5:G8">
     <x:cfRule type="expression" dxfId="0" priority="1">
@@ -598,6 +823,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9cf4c2540504100"/>
 </x:worksheet>
 </file>
 
@@ -608,6 +834,8 @@
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="11.4399995803833" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="18" hidden="0" customHeight="1">
@@ -616,6 +844,8 @@
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
+      <x:c r="E1" s="4"/>
     </x:row>
     <x:row r="2" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A2" s="9" t="str">
@@ -623,6 +853,8 @@
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
+      <x:c r="D2" s="9"/>
+      <x:c r="E2" s="9"/>
     </x:row>
     <x:row r="3"/>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
@@ -714,11 +946,43 @@
       </x:c>
     </x:row>
     <x:row r="12"/>
-    <x:row r="13"/>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="60" t="str">
+        <x:v>电子签署（测试）｜工程质量测试专用章</x:v>
+      </x:c>
+      <x:c r="B13" s="61"/>
+      <x:c r="C13" s="61"/>
+      <x:c r="D13" s="61"/>
+      <x:c r="E13" s="62"/>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="63"/>
+      <x:c r="B14" s="64"/>
+      <x:c r="C14" s="64"/>
+      <x:c r="D14" s="64"/>
+      <x:c r="E14" s="65"/>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="63"/>
+      <x:c r="B15" s="64"/>
+      <x:c r="C15" s="64"/>
+      <x:c r="D15" s="64"/>
+      <x:c r="E15" s="65"/>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="66"/>
+      <x:c r="B16" s="67"/>
+      <x:c r="C16" s="67"/>
+      <x:c r="D16" s="67"/>
+      <x:c r="E16" s="68"/>
+    </x:row>
+    <x:row r="17"/>
+    <x:row r="18"/>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:C1"/>
-    <x:mergeCell ref="A2:C2"/>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A13:C13"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="A5:C11">
     <x:cfRule type="expression" dxfId="2" priority="1">
@@ -729,5 +993,6 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9aa053786eeb4f1f"/>
 </x:worksheet>
 </file>